--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T09:15:08+00:00</t>
+    <t>2026-06-15T12:03:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:03:07+00:00</t>
+    <t>2026-06-15T12:05:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:05:54+00:00</t>
+    <t>2026-06-15T12:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:19:26+00:00</t>
+    <t>2026-06-15T12:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:25:11+00:00</t>
+    <t>2026-06-15T15:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T15:22:45+00:00</t>
+    <t>2026-06-29T09:12:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:12:00+00:00</t>
+    <t>2026-06-29T15:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:18:50+00:00</t>
+    <t>2026-07-20T14:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:34+00:00</t>
+    <t>2026-07-20T14:36:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:36:58+00:00</t>
+    <t>2026-07-20T15:18:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:18:49+00:00</t>
+    <t>2026-07-20T15:21:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:21:00+00:00</t>
+    <t>2026-07-20T15:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:29:23+00:00</t>
+    <t>2026-07-20T15:43:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:43:25+00:00</t>
+    <t>2026-07-21T08:10:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:10:44+00:00</t>
+    <t>2026-07-31T14:40:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
+++ b/nr-doc-core-condition/ig/StructureDefinition-fr-core-organization-discipline-equipement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:40:09+00:00</t>
+    <t>2026-09-07T15:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
